--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-parent-document.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-parent-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T14:51:40+00:00</t>
+    <t>2025-01-14T21:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-parent-document.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-parent-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T21:51:01+00:00</t>
+    <t>2025-01-15T14:08:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-parent-document.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-parent-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="148">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-15T14:08:36+00:00</t>
+    <t>2025-01-17T15:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,6 +311,10 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
+</t>
   </si>
   <si>
     <t>ParentDocument.typeId.nullFlavor</t>
@@ -1319,7 +1323,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1327,10 +1331,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1428,17 +1432,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -1456,11 +1460,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1511,7 +1515,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1531,17 +1535,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1559,11 +1563,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1614,7 +1618,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1634,17 +1638,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1662,11 +1666,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1675,7 +1679,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -1717,7 +1721,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1737,17 +1741,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1765,11 +1769,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1820,7 +1824,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1840,10 +1844,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1870,7 +1874,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1921,7 +1925,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -1941,10 +1945,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1978,7 +1982,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -2000,7 +2004,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2018,7 +2022,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2038,10 +2042,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2075,7 +2079,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2097,7 +2101,7 @@
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2115,7 +2119,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2135,10 +2139,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2164,7 +2168,7 @@
         <v>95</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -2216,7 +2220,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -2236,10 +2240,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2252,7 +2256,7 @@
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>74</v>
@@ -2337,17 +2341,17 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>80</v>
@@ -2365,11 +2369,11 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2420,7 +2424,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2440,17 +2444,17 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>80</v>
@@ -2468,11 +2472,11 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2523,7 +2527,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -2543,17 +2547,17 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>75</v>
@@ -2571,13 +2575,13 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2628,7 +2632,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2648,17 +2652,17 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>80</v>
@@ -2676,13 +2680,13 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2733,7 +2737,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -2753,10 +2757,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2779,7 +2783,7 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -2808,11 +2812,11 @@
         <v>74</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>74</v>
@@ -2830,7 +2834,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -2850,10 +2854,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2876,7 +2880,7 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
@@ -2929,7 +2933,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -2949,10 +2953,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3028,7 +3032,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3048,10 +3052,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3074,7 +3078,7 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -3127,7 +3131,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-parent-document.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-parent-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:05:21+00:00</t>
+    <t>2025-02-03T10:34:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-parent-document.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-parent-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T10:34:19+00:00</t>
+    <t>2025-02-05T14:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-parent-document.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-parent-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:18:33+00:00</t>
+    <t>2025-02-05T15:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-parent-document.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-parent-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:17:43+00:00</t>
+    <t>2025-02-05T15:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Document de référence.</t>
+    <t>Document de référence</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-parent-document.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-parent-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:35:39+00:00</t>
+    <t>2025-02-06T13:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Document de référence</t>
+    <t>L'élément de l'en-tête du CDA parentDocument permet de représenter le document de référence.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-parent-document.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-parent-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T13:21:10+00:00</t>
+    <t>2025-02-06T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
